--- a/output/pdf_financials_xlsx/CPER.xlsx
+++ b/output/pdf_financials_xlsx/CPER.xlsx
@@ -2786,19 +2786,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.103451</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.7105</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.77085</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.30485</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.410695</v>
       </c>
     </row>
     <row r="93">
@@ -4712,7 +4712,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -5862,7 +5866,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CPER.xlsx
+++ b/output/pdf_financials_xlsx/CPER.xlsx
@@ -705,16 +705,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.169862</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.278526</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.208042</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.07656300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1130,16 +1130,16 @@
         <v>-4.630346</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.207456</v>
+        <v>-4.377318</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.730349</v>
+        <v>-3.008875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.442187</v>
+        <v>-3.650229</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.820797</v>
+        <v>-3.89736</v>
       </c>
     </row>
     <row r="28">
@@ -1180,16 +1180,16 @@
         <v>-4.601696</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.140906</v>
+        <v>-4.310768</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.655815</v>
+        <v>-2.934341</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.366448</v>
+        <v>-3.57449</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.820797</v>
+        <v>-3.89736</v>
       </c>
     </row>
     <row r="30">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>6.152979</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.93922</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.015143</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>5.594656</v>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>6.152979</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.93922</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.015143</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>5.594656</v>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.152979</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.206415</v>
+        <v>0.267195</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.187726</v>
+        <v>0.172583</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.151313</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">

--- a/output/pdf_financials_xlsx/CPER.xlsx
+++ b/output/pdf_financials_xlsx/CPER.xlsx
@@ -577,19 +577,19 @@
         <v>0.021043</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.455482</v>
+        <v>0.523732</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.9681419999999999</v>
+        <v>1.049142</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.796911</v>
+        <v>0.833161</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.567316</v>
+        <v>0.604816</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.661401</v>
+        <v>0.697167</v>
       </c>
     </row>
     <row r="8">
@@ -2145,19 +2145,19 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.039178</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
@@ -2990,22 +2990,22 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001338</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.087745</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.035907</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.014372</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018748</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.06647400000000001</v>
       </c>
     </row>
     <row r="102">
@@ -3115,22 +3115,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.041498</v>
+        <v>0.04016</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.076261</v>
+        <v>-0.011484</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.010773</v>
+        <v>0.04668</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.023177</v>
+        <v>0.037549</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.004185</v>
+        <v>-0.022933</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.021283</v>
+        <v>-0.087757</v>
       </c>
     </row>
     <row r="107">
@@ -3243,19 +3243,19 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.053584</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03656</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040202</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03731</v>
       </c>
     </row>
     <row r="112">
@@ -3830,19 +3830,19 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.053584</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03656</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040202</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03731</v>
       </c>
     </row>
     <row r="135">
@@ -3855,19 +3855,19 @@
         <v>-0.045561</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.576055</v>
+        <v>-2.629639</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.394809</v>
+        <v>-3.431369</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.593237</v>
+        <v>-2.633439</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-2.823344</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-3.801808</v>
+        <v>-3.839118</v>
       </c>
     </row>
   </sheetData>
@@ -3881,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6070,10 +6070,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="5" t="n">
+        <v>-4.630346</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>-4.207456</v>
@@ -6274,7 +6272,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6440,7 +6442,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -7258,7 +7264,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>-0.001338</v>
       </c>
@@ -7306,10 +7316,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="5" t="n">
+        <v>6.152979</v>
       </c>
       <c r="G78" s="5" t="n">
         <v>5.93922</v>
@@ -7352,10 +7360,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F79" s="5" t="n">
+        <v>5.93922</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>7.015143</v>
@@ -7562,20 +7568,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Year-ended              incorporation on</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2021 December</t>
+          <t>Deferred financing costs</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.00202</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.103569</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -7606,24 +7614,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>-0.07072100000000001</v>
+          <t>Deposit on lease</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-4.630346</v>
+        <v>-0.004603</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -7654,22 +7660,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
+          <t>Supplemental Schedule of Non-Cash Investing and Financing Activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Acquisition of Georgina</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>-0.051677</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred financing fee in accounts payable $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.069109</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -7700,22 +7710,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Year-ended              incorporation on</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deferred financing costs</t>
+          <t>2021 December</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.103569</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -7746,22 +7754,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deposit on lease</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>-0.07072100000000001</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.004603</v>
+        <v>-4.630346</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -7792,26 +7802,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cash, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>6.152979</v>
+          <t>Acquisition of Georgina</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-0.051677</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -7847,19 +7853,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash, end of the period $</t>
+          <t>Cash, beginning of the period</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>6.152979</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>5.93922</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -7890,22 +7898,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supplemental Schedule of Non-Cash Investing and Financing Activities</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Shares issued for property acquisition $</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Cash, end of the period $</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
-        <v>0.4635</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.152979</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>5.93922</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -7941,16 +7951,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shares issue costs included in accounts payable and accrued liabilities $</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Shares issued for property acquisition $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
-        <v>0.015</v>
+        <v>0.4635</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7986,12 +7992,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deferred financing costs included in accounts payable and</t>
+          <t>Supplemental Schedule of Non-Cash Investing and Financing Activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Deferred financing costs included in accounts payable and accrued liabilities $</t>
+          <t>Shares issue costs included in accounts payable and accrued liabilities $</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7999,13 +8005,13 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>0.069109</v>
+      <c r="E93" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -8031,29 +8037,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Deferred financing costs included in accounts payable and</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Depreciation, amortization and accretion 4,6,7 $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Deferred financing costs included in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" s="5" t="n">
+        <v>0.069109</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -8065,11 +8073,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n">
-        <v>0.075739</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>0.052046</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -8085,33 +8097,35 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bank charges and interest</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Depreciation, amortization and accretion 4,6,7 $</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>0.010846</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>0.017954</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>0.012072</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.005323</v>
+        <v>0.075739</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.005681</v>
+        <v>0.052046</v>
       </c>
     </row>
     <row r="96">
@@ -8127,29 +8141,33 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Director fees 9</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Bank charges and interest</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.06825000000000001</v>
+        <v>0.010846</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.081</v>
+        <v>0.017954</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.03625</v>
+        <v>0.012072</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.005323</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.035766</v>
+        <v>0.005681</v>
       </c>
     </row>
     <row r="97">
@@ -8165,33 +8183,33 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Exploration expenditures 4,9</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Director fees 9</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>0.06825000000000001</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.081</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>1.757476</v>
+        <v>0.03625</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>1.859567</v>
+        <v>0.0375</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>2.41117</v>
+        <v>0.035766</v>
       </c>
     </row>
     <row r="98">
@@ -8207,33 +8225,33 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Management and consulting fees 9</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration expenditures 4,9</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>0.355125</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0.530625</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.542085</v>
+        <v>1.757476</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.38</v>
+        <v>1.859567</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>0.52794</v>
+        <v>2.41117</v>
       </c>
     </row>
     <row r="99">
@@ -8249,29 +8267,33 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Marketing and IR</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Management and consulting fees 9</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.501265</v>
+        <v>0.355125</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.629183</v>
+        <v>0.530625</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.131314</v>
+        <v>0.542085</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.208107</v>
+        <v>0.38</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>0.438554</v>
+        <v>0.52794</v>
       </c>
     </row>
     <row r="100">
@@ -8287,33 +8309,29 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Marketing and IR</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.070949</v>
+        <v>0.501265</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.3305</v>
+        <v>0.629183</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.210557</v>
+        <v>0.131314</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0.145616</v>
+        <v>0.208107</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.10514</v>
+        <v>0.438554</v>
       </c>
     </row>
     <row r="101">
@@ -8329,12 +8347,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8343,19 +8361,19 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.089336</v>
+        <v>0.070949</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.287727</v>
+        <v>0.3305</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.150214</v>
+        <v>0.210557</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0.111455</v>
+        <v>0.145616</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0.075666</v>
+        <v>0.10514</v>
       </c>
     </row>
     <row r="102">
@@ -8371,29 +8389,33 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Share-based compensation 8,9</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>2.103451</v>
+        <v>0.089336</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.6070489999999999</v>
+        <v>0.287727</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.015716</v>
+        <v>0.150214</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.56289</v>
+        <v>0.111455</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.053329</v>
+        <v>0.075666</v>
       </c>
     </row>
     <row r="103">
@@ -8409,33 +8431,29 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based compensation 8,9</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.029408</v>
+        <v>2.103451</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.107017</v>
+        <v>0.6070489999999999</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.044269</v>
+        <v>0.015716</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.56289</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>0.028321</v>
+        <v>0.053329</v>
       </c>
     </row>
     <row r="104">
@@ -8451,31 +8469,33 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Travel and conference</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="5" t="n">
+        <v>0.029408</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.09488099999999999</v>
+        <v>0.107017</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.114032</v>
+        <v>0.044269</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>0.189531</v>
+        <v>0.0417</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>0.174805</v>
+        <v>0.028321</v>
       </c>
     </row>
     <row r="105">
@@ -8491,33 +8511,31 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Travel and conference</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n">
-        <v>4.601593</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>4.351894</v>
+        <v>0.09488099999999999</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>3.088519</v>
+        <v>0.114032</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>3.617428</v>
+        <v>0.189531</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>3.908418</v>
+        <v>0.174805</v>
       </c>
     </row>
     <row r="106">
@@ -8528,17 +8546,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8546,22 +8564,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="5" t="n">
+        <v>4.601593</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.169862</v>
+        <v>4.351894</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.278526</v>
+        <v>3.088519</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.208042</v>
+        <v>3.617428</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>0.07656300000000001</v>
+        <v>3.908418</v>
       </c>
     </row>
     <row r="107">
@@ -8577,12 +8593,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Other income 4</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8595,21 +8611,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="5" t="n">
+        <v>0.169862</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.118813</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.278526</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0.208042</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>0.06306299999999999</v>
+        <v>0.07656300000000001</v>
       </c>
     </row>
     <row r="108">
@@ -8625,12 +8637,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Other income 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8638,20 +8650,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>-0.028753</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>-0.025424</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>-0.039169</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>-0.032801</v>
+        <v>0.118813</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>-0.052005</v>
+        <v>0.06306299999999999</v>
       </c>
     </row>
     <row r="109">
@@ -8667,12 +8685,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8681,19 +8699,19 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>-4.630346</v>
+        <v>-0.028753</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-4.207456</v>
+        <v>-0.025424</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-2.730349</v>
+        <v>-0.039169</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>-3.442187</v>
+        <v>-0.032801</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>-3.820797</v>
+        <v>-0.052005</v>
       </c>
     </row>
     <row r="110">
@@ -8704,38 +8722,38 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>-4.630346</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-4.207456</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>67.57952899999999</v>
+        <v>-2.730349</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>86.176576</v>
+        <v>-3.442187</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>101.970182</v>
+        <v>-3.820797</v>
       </c>
     </row>
     <row r="111">
@@ -8746,12 +8764,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shares       Amount       Reserves            Deficit         Total</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 85,996,162 $ 15,115,257 $ 2,770,850 $</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8770,16 +8788,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H111" s="5" t="n">
+        <v>67.57952899999999</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>6.247235</v>
+        <v>86.176576</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>-11.638872</v>
+        <v>101.970182</v>
       </c>
     </row>
     <row r="112">
@@ -8795,7 +8811,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 562,890</t>
+          <t>Balance, December 31, 2023 85,996,162 $ 15,115,257 $ 2,770,850 $</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -8820,12 +8836,10 @@
         </is>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.56289</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.247235</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>-11.638872</v>
       </c>
     </row>
     <row r="113">
@@ -8841,7 +8855,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,025,467 251,508 (8,452)</t>
+          <t>Share-based compensation - - 562,890</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -8866,7 +8880,7 @@
         </is>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.243056</v>
+        <v>0.56289</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -8887,7 +8901,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Options exercised 300,000 56,438 (20,438)</t>
+          <t>Warrants exercised 2,025,467 251,508 (8,452)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8912,7 +8926,7 @@
         </is>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0.036</v>
+        <v>0.243056</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -8933,14 +8947,10 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Options exercised 300,000 56,438 (20,438)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -8962,10 +8972,12 @@
         </is>
       </c>
       <c r="I115" s="5" t="n">
-        <v>-3.442187</v>
-      </c>
-      <c r="J115" s="5" t="n">
-        <v>-3.442187</v>
+        <v>0.036</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -8981,10 +8993,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 88,321,629 $ 15,423,203 $ 3,304,850 $</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9006,10 +9022,10 @@
         </is>
       </c>
       <c r="I116" s="5" t="n">
-        <v>3.646994</v>
+        <v>-3.442187</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>-15.081059</v>
+        <v>-3.442187</v>
       </c>
     </row>
     <row r="117">
@@ -9025,7 +9041,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 29,415,517 2,500,319 -</t>
+          <t>Balance, December 31, 2024 88,321,629 $ 15,423,203 $ 3,304,850 $</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -9050,12 +9066,10 @@
         </is>
       </c>
       <c r="I117" s="5" t="n">
-        <v>2.500319</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.646994</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>-15.081059</v>
       </c>
     </row>
     <row r="118">
@@ -9071,7 +9085,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (80,676) -</t>
+          <t>Shares issued for private placement 29,415,517 2,500,319 -</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9096,7 +9110,7 @@
         </is>
       </c>
       <c r="I118" s="5" t="n">
-        <v>-0.080676</v>
+        <v>2.500319</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -9117,7 +9131,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Share issue costs – warrants - (52,516) 52,516</t>
+          <t>Share issue costs – cash - (80,676) -</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9141,10 +9155,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="5" t="n">
+        <v>-0.080676</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -9165,7 +9177,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 53,329</t>
+          <t>Share issue costs – warrants - (52,516) 52,516</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9189,8 +9201,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="5" t="n">
-        <v>0.053329</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -9211,7 +9225,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Warrants exercised 1,220,000 146,400 -</t>
+          <t>Share-based compensation - - 53,329</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9236,7 +9250,7 @@
         </is>
       </c>
       <c r="I121" s="5" t="n">
-        <v>0.1464</v>
+        <v>0.053329</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -9257,7 +9271,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 118,957,146 $ 17,936,730 $ 3,410,695 $</t>
+          <t>Warrants exercised 1,220,000 146,400 -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9282,10 +9296,12 @@
         </is>
       </c>
       <c r="I122" s="5" t="n">
-        <v>2.445569</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>-18.901856</v>
+        <v>0.1464</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -9296,19 +9312,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares       Amount       Reserves            Deficit         Total</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 6,7 $</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2025 118,957,146 $ 17,936,730 $ 3,410,695 $</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -9324,16 +9336,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="5" t="n">
-        <v>0.074534</v>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I123" s="5" t="n">
-        <v>0.075739</v>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.445569</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>-18.901856</v>
       </c>
     </row>
     <row r="124">
@@ -9344,15 +9356,19 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shares     Amount           Reserves           Deficit           Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Depreciation and amortization 6,7 $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -9369,10 +9385,10 @@
         </is>
       </c>
       <c r="H124" s="5" t="n">
-        <v>7.629024</v>
+        <v>0.074534</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>-8.908523000000001</v>
+        <v>0.075739</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -9393,7 +9409,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 19,770,797 1,383,956 -</t>
+          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -9413,12 +9429,10 @@
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>1.383956</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.629024</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>-8.908523000000001</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -9439,7 +9453,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (51,112) -</t>
+          <t>Shares issued for private placement 19,770,797 1,383,956 -</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -9459,7 +9473,7 @@
         </is>
       </c>
       <c r="H126" s="5" t="n">
-        <v>-0.051112</v>
+        <v>1.383956</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9485,7 +9499,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Share issue costs - warrants - (44,634) 44,634</t>
+          <t>Share issue costs – cash - (51,112) -</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9504,10 +9518,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H127" s="5" t="n">
+        <v>-0.051112</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9533,7 +9545,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 15,716</t>
+          <t>Share issue costs - warrants - (44,634) 44,634</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -9552,8 +9564,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H128" s="5" t="n">
-        <v>0.015716</v>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -9579,14 +9593,10 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 15,716</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -9603,10 +9613,12 @@
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>-2.730349</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>-2.730349</v>
+        <v>0.015716</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -9627,10 +9639,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 85,996,162 $ 15,115,257 $ 2,770,850 $</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -9647,10 +9663,10 @@
         </is>
       </c>
       <c r="H130" s="5" t="n">
-        <v>6.247235</v>
+        <v>-2.730349</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>-11.638872</v>
+        <v>-2.730349</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -9671,7 +9687,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 562,890</t>
+          <t>Balance, December 31, 2023 85,996,162 $ 15,115,257 $ 2,770,850 $</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9691,12 +9707,10 @@
         </is>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0.56289</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.247235</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>-11.638872</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -9717,7 +9731,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,025,467 251,508 (8,452)</t>
+          <t>Share-based compensation - - 562,890</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9737,7 +9751,7 @@
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.243056</v>
+        <v>0.56289</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -9763,7 +9777,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Options exercised 300,000 56,438 (20,438)</t>
+          <t>Warrants exercised 2,025,467 251,508 (8,452)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -9783,7 +9797,7 @@
         </is>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0.036</v>
+        <v>0.243056</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -9809,7 +9823,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 88,321,629 $ 15,423,203 $ 3,304,850 $</t>
+          <t>Options exercised 300,000 56,438 (20,438)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -9829,10 +9843,12 @@
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>3.646994</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>-15.081059</v>
+        <v>0.036</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9848,37 +9864,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares     Amount           Reserves           Deficit           Total</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Depreciation 6,7 $</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2024 88,321,629 $ 15,423,203 $ 3,304,850 $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>0.02865</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>0.06655</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.074534</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.646994</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>-15.081059</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9899,23 +9913,27 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Exploration expenditures 4</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>Depreciation 6,7 $</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>1.344313</v>
+        <v>0.02865</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>1.599408</v>
+        <v>0.06655</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>1.757476</v>
+        <v>0.074534</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -9936,32 +9954,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Exploration expenditures 4</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>51.090369</v>
+        <v>1.344313</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>65.83988600000001</v>
+        <v>1.599408</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>67.57952899999999</v>
+        <v>1.757476</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -9982,30 +9996,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Shares       Amount       Reserves          Deficit           Total</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $ 2,103,451 $</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F138" s="5" t="n">
+        <v>51.090369</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>6.668413</v>
+        <v>65.83988600000001</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>-4.701067</v>
+        <v>67.57952899999999</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -10031,7 +10047,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 10,000,000 5,000,000 -</t>
+          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $ 2,103,451 $</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -10046,12 +10062,10 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.668413</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-4.701067</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -10077,7 +10091,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (438,982) -</t>
+          <t>Shares issued for private placement 10,000,000 5,000,000 -</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -10092,7 +10106,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-0.438982</v>
+        <v>5</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -10123,7 +10137,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share issue costs– corporate finance fee 50,000 - -</t>
+          <t>Share issue costs – cash - (438,982) -</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -10137,10 +10151,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G141" s="5" t="n">
+        <v>-0.438982</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -10171,7 +10183,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 607,049</t>
+          <t>Share issue costs– corporate finance fee 50,000 - -</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10185,8 +10197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G142" s="5" t="n">
-        <v>0.6070489999999999</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -10217,14 +10231,10 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based compensation - - 607,049</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -10236,10 +10246,12 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>-4.207456</v>
-      </c>
-      <c r="H143" s="5" t="n">
-        <v>-4.207456</v>
+        <v>0.6070489999999999</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -10265,10 +10277,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -10280,10 +10296,10 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>7.629024</v>
+        <v>-4.207456</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>-8.908523000000001</v>
+        <v>-4.207456</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -10309,7 +10325,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 19,770,797 1,383,956 -</t>
+          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10324,12 +10340,10 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1.383956</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.629024</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-8.908523000000001</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -10355,7 +10369,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (51,112) -</t>
+          <t>Shares issued for private placement 19,770,797 1,383,956 -</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -10370,7 +10384,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>-0.051112</v>
+        <v>1.383956</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -10401,7 +10415,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Share issue costs - warrants - (44,634) 44,634</t>
+          <t>Share issue costs – cash - (51,112) -</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -10415,10 +10429,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G147" s="5" t="n">
+        <v>-0.051112</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -10449,7 +10461,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 15,716</t>
+          <t>Share issue costs - warrants - (44,634) 44,634</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -10463,8 +10475,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G148" s="5" t="n">
-        <v>0.015716</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -10495,7 +10509,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 85,996,162 $15,115,257 $ 2,770,850 $</t>
+          <t>Share-based compensation - - 15,716</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -10510,10 +10524,12 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>6.247235</v>
-      </c>
-      <c r="H149" s="5" t="n">
-        <v>-11.638872</v>
+        <v>0.015716</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -10534,12 +10550,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Shares      Amount       Reserves          Deficit           Total</t>
+          <t>Shares       Amount       Reserves          Deficit           Total</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 44,228,025 $ 6,698,717 $ - $</t>
+          <t>Balance, December 31, 2023 85,996,162 $15,115,257 $ 2,770,850 $</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -10548,16 +10564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F150" s="5" t="n">
-        <v>6.627996</v>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-0.07072100000000001</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.247235</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>-11.638872</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -10583,7 +10599,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 11,947,340 2,645,676 -</t>
+          <t>Balance, December 31, 2020 44,228,025 $ 6,698,717 $ - $</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -10593,12 +10609,10 @@
         </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>2.645676</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.627996</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>-0.07072100000000001</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -10629,7 +10643,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 2,103,451</t>
+          <t>Shares issued for private placements 11,947,340 2,645,676 -</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -10639,7 +10653,7 @@
         </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>2.103451</v>
+        <v>2.645676</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -10675,7 +10689,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (78,364) -</t>
+          <t>Share-based compensation - - 2,103,451</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -10685,7 +10699,7 @@
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>-0.078364</v>
+        <v>2.103451</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -10721,24 +10735,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs – cash - (78,364) -</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>-4.630346</v>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>-4.630346</v>
+        <v>-0.078364</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10769,20 +10781,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $2,103,451 $</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>6.668413</v>
+        <v>-4.630346</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>-4.701067</v>
+        <v>-4.630346</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10813,7 +10829,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $ 2,103,451 $</t>
+          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $2,103,451 $</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -10857,7 +10873,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 10,000,000 5,000,000 -</t>
+          <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $ 2,103,451 $</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -10867,12 +10883,10 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.668413</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>-4.701067</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10903,7 +10917,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (438,982) -</t>
+          <t>Shares issued for private placement 10,000,000 5,000,000 -</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -10913,7 +10927,7 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>-0.438982</v>
+        <v>5</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -10949,7 +10963,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Share issue costs– corporate finance fee 50,000 - -</t>
+          <t>Share issue costs – cash - (438,982) -</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -10958,10 +10972,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F159" s="5" t="n">
+        <v>-0.438982</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -10997,7 +11009,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 607,049</t>
+          <t>Share issue costs– corporate finance fee 50,000 - -</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -11006,8 +11018,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F160" s="5" t="n">
-        <v>0.6070489999999999</v>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -11043,7 +11057,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
+          <t>Share-based compensation - - 607,049</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -11053,10 +11067,12 @@
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>7.629024</v>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>-8.908523000000001</v>
+        <v>0.6070489999999999</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -11082,25 +11098,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Shares      Amount       Reserves          Deficit           Total</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>December 31, 2021 December</t>
+          <t>Balance, December 31, 2022 66,225,365 $ 13,827,047 $ 2,710,500 $</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>0.00202</v>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.629024</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>-8.908523000000001</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -11126,22 +11142,20 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Depreciation and amortization expense (Note 6 and 7) $</t>
+          <t>December 31, 2021 December</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E163" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>0.02865</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -11177,19 +11191,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bank charges and interest (Note 7)</t>
+          <t>Depreciation and amortization expense (Note 6 and 7) $</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="n">
-        <v>0.000918</v>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.010846</v>
+        <v>0.02865</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -11225,17 +11241,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Director Fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank charges and interest (Note 7)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>0.000918</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>0.06825000000000001</v>
+        <v>0.010846</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -11271,15 +11289,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 9)</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>0.026757</v>
+          <t>Director Fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>1.344313</v>
+        <v>0.06825000000000001</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -11315,19 +11339,15 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (Note 9)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="n">
-        <v>0.002147</v>
+        <v>0.026757</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.028753</v>
+        <v>1.344313</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -11363,19 +11383,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Management and consulting fees (Note 10)</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0.016109</v>
+        <v>0.002147</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.355125</v>
+        <v>0.028753</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -11411,17 +11431,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Marketing and IR</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Management and consulting fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>0.016109</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>0.501265</v>
+        <v>0.355125</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -11457,19 +11479,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E170" s="5" t="n">
-        <v>0.004344</v>
+          <t>Marketing and IR</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.070949</v>
+        <v>0.501265</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -11505,19 +11525,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0.019856</v>
+        <v>0.004344</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>0.089336</v>
+        <v>0.070949</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -11553,17 +11573,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 8 and 10)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>0.019856</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>2.103451</v>
+        <v>0.089336</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -11599,19 +11621,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="n">
-        <v>0.00059</v>
+          <t>Share-based compensation (Note 8 and 10)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F173" s="5" t="n">
-        <v>0.029408</v>
+        <v>2.103451</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -11647,19 +11667,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>-0.07072100000000001</v>
+        <v>0.00059</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-4.630346</v>
+        <v>0.029408</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -11695,19 +11715,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Loss for the period $</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.07072100000000001</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-4.630346</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -11743,19 +11763,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>14.051002</v>
+        <v>-1e-08</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>51.090369</v>
+        <v>-9e-08</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -11786,24 +11806,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Shares      Amount       Reserves          Deficit          Total</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Balance, July 21, 2020 (incorporation) - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding, basic</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>14.051002</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>51.090369</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -11839,7 +11859,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Shares issued on incorporation 2 - -</t>
+          <t>Balance, July 21, 2020 (incorporation) - $ - $ - $</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -11887,12 +11907,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Shares issued for property acquisition 10,300,000 463,500 -</t>
+          <t>Shares issued on incorporation 2 - -</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
-      <c r="E179" s="5" t="n">
-        <v>0.4635</v>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -11933,12 +11955,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Shares issued for private placements 33,928,023 6,452,587 -</t>
+          <t>Shares issued for property acquisition 10,300,000 463,500 -</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" s="5" t="n">
-        <v>6.452587</v>
+        <v>0.4635</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -11979,12 +12001,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (217,370) -</t>
+          <t>Shares issued for private placements 33,928,023 6,452,587 -</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" s="5" t="n">
-        <v>-0.21737</v>
+        <v>6.452587</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -12025,19 +12047,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs – cash - (217,370) -</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" s="5" t="n">
-        <v>-0.07072100000000001</v>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>-0.07072100000000001</v>
+        <v>-0.21737</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -12073,12 +12093,16 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 44,228,025 $ 6,698,717 $ - $</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E183" s="5" t="n">
-        <v>6.627996</v>
+        <v>-0.07072100000000001</v>
       </c>
       <c r="F183" s="5" t="n">
         <v>-0.07072100000000001</v>
@@ -12117,17 +12141,15 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 11,947,340 2,645,676 -</t>
+          <t>Balance, December 31, 2020 44,228,025 $ 6,698,717 $ - $</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" s="5" t="n">
-        <v>2.645676</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.627996</v>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>-0.07072100000000001</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -12163,12 +12185,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 2,103,451</t>
+          <t>Shares issued for private placement 11,947,340 2,645,676 -</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" s="5" t="n">
-        <v>2.103451</v>
+        <v>2.645676</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -12209,12 +12231,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Share issue costs – cash - (78,364) -</t>
+          <t>Share-based compensation - - 2,103,451</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" s="5" t="n">
-        <v>-0.078364</v>
+        <v>2.103451</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -12255,19 +12277,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs – cash - (78,364) -</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" s="5" t="n">
-        <v>-4.630346</v>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>-4.630346</v>
+        <v>-0.078364</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -12303,32 +12323,80 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>-4.630346</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>-4.630346</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Shares      Amount       Reserves          Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>Balance, December 31, 2021 56,175,365 $ 9,266,029 $ 2,103,451 $</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" s="5" t="n">
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
         <v>6.668413</v>
       </c>
-      <c r="F188" s="5" t="n">
+      <c r="F189" s="5" t="n">
         <v>-4.701067</v>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
